--- a/Configs/GameConfig/Datas/AttackConfig.xlsx
+++ b/Configs/GameConfig/Datas/AttackConfig.xlsx
@@ -2,39 +2,375 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="25600" windowHeight="12080" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="21">
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -42,15 +378,305 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -403,7 +1029,6 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -413,8 +1038,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:M10"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
+  <cols>
+    <col width="8.54545454545454" customWidth="1" min="1" max="1"/>
+    <col width="7.54545454545455" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="10.6363636363636" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="29.8181818181818" customWidth="1" min="7" max="8"/>
+    <col width="27.5454545454545" customWidth="1" min="9" max="9"/>
+    <col width="19.6363636363636" customWidth="1" min="10" max="10"/>
+    <col width="32" customWidth="1" min="11" max="12"/>
+    <col width="34.2727272727273" customWidth="1" min="13" max="14"/>
+    <col width="33.1818181818182" customWidth="1" min="15" max="15"/>
+    <col width="32" customWidth="1" min="16" max="16"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -449,52 +1089,37 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>PowerScaleMin</t>
+          <t>PowerScale</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>PowerScaleMax</t>
+          <t>FlatPower</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>FlatPower</t>
+          <t>DamageKind</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>DamageKind</t>
+          <t>Knockback</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>KnockbackX</t>
+          <t>WsGain</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>KnockbackY</t>
+          <t>HitProtect</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>WsGainMin</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>WsGainMax</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>HitProtect</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>HitInterval</t>
+          <t>Interval</t>
         </is>
       </c>
     </row>
@@ -538,50 +1163,35 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>vector2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Battle.DamageKind</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>vector2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>vector2i</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>int</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Battle.DamageKind</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
       <c r="M3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
         <is>
           <t>float</t>
         </is>
@@ -627,52 +1237,37 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>攻击力倍率下限(乘英雄攻击)</t>
+          <t>攻击力倍率范围(乘英雄攻击,X=下限,Y=上限)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>攻击力倍率上限(乘英雄攻击)</t>
+          <t>固定攻击力(不与属性挂钩)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>固定攻击力(不与属性挂钩)</t>
+          <t>伤害类型</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>伤害类型</t>
+          <t>击退(旧 hurtBack[0]/[1],X=横向,Y=纵向)</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>击退横向分量(旧 hurtBack[0])</t>
+          <t>命中获得无双值范围(旧 WSValue,X=下限,Y=上限)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>击退纵向分量(旧 hurtBack[1])</t>
+          <t>受击保护累计值(旧 HitProtect)</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>命中获得无双值下限(旧 WSValue)</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>命中获得无双值上限(旧 WSValue)</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>受击保护累计值(旧 HitProtect)</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>同招连击间隔秒(旧 HitInterv)</t>
+          <t>本段最短停留秒(动画不足时补足,即普攻之间的间隔)</t>
         </is>
       </c>
     </row>
@@ -700,37 +1295,34 @@
           <t>attack_1</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>1</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1,1.2</t>
+        </is>
       </c>
       <c r="H6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="I6" t="n">
         <v>0</v>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Physics</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>2</v>
+          <t>2,0</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>3,5</t>
+        </is>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
-      </c>
-      <c r="N6" t="n">
-        <v>5</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="7">
@@ -757,37 +1349,34 @@
           <t>attack_2</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>0.9</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.9,1.1</t>
+        </is>
       </c>
       <c r="H7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="I7" t="n">
         <v>0</v>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Physics</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>2</v>
+          <t>2,0</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>3,5</t>
+        </is>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
-      </c>
-      <c r="N7" t="n">
-        <v>5</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="8">
@@ -814,37 +1403,34 @@
           <t>attack_3</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>1</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1,1.2</t>
+        </is>
       </c>
       <c r="H8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="I8" t="n">
         <v>0</v>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Physics</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>2</v>
+          <t>2,0</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>3,5</t>
+        </is>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
-      </c>
-      <c r="N8" t="n">
-        <v>5</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="9">
@@ -871,37 +1457,34 @@
           <t>attack_4</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>1.2</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1.2,1.4</t>
+        </is>
       </c>
       <c r="H9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="I9" t="n">
         <v>0</v>
       </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Physics</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>6</v>
+          <t>6,-5</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>3,5</t>
+        </is>
       </c>
       <c r="L9" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
-      </c>
-      <c r="N9" t="n">
-        <v>5</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="10">
@@ -928,37 +1511,34 @@
           <t>attack_1</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
         <v>10</v>
       </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Physics</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>-3</v>
+          <t>-3,-6</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
       </c>
       <c r="L10" t="n">
-        <v>-6</v>
+        <v>10</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>10</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/AttackConfig.xlsx
+++ b/Configs/GameConfig/Datas/AttackConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="25600" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="95">
   <si>
     <t>##var</t>
   </si>
@@ -83,6 +83,12 @@
     <t>AiWeight</t>
   </si>
   <si>
+    <t>HitBoxOffset</t>
+  </si>
+  <si>
+    <t>HitBoxSize</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -140,7 +146,7 @@
     <t>伤害类型</t>
   </si>
   <si>
-    <t>击退(旧 hurtBack[0]/[1],X=横向,Y=纵向,写法 2,0)</t>
+    <t>击退(X&gt;0=远离攻击者,Y&lt;0=向上;单位同旧 hurtBack,乘 BattleConfig.KnockbackScale* 换算 px/s,写法 2,0)</t>
   </si>
   <si>
     <t>命中获得无双值范围(旧 WSValue,X=下限,Y=上限,写法 3,5)</t>
@@ -167,6 +173,12 @@
     <t>AI 选招权重(怪物 AI 用;英雄普攻填 0)</t>
   </si>
   <si>
+    <t>判定盒中心相对角色原点(X&gt;0=前方,Y 向下为正,写法 45,-17)</t>
+  </si>
+  <si>
+    <t>判定盒矩形尺寸 px(写法 152,186)</t>
+  </si>
+  <si>
     <t>role1.hit1</t>
   </si>
   <si>
@@ -200,6 +212,12 @@
     <t>Wukong</t>
   </si>
   <si>
+    <t>45,-17</t>
+  </si>
+  <si>
+    <t>152,186</t>
+  </si>
+  <si>
     <t>role1.hit2</t>
   </si>
   <si>
@@ -218,6 +236,12 @@
     <t>WukongAttack2</t>
   </si>
   <si>
+    <t>42.25,41.5</t>
+  </si>
+  <si>
+    <t>133.5,43</t>
+  </si>
+  <si>
     <t>role1.hit3</t>
   </si>
   <si>
@@ -230,6 +254,12 @@
     <t>attack_3</t>
   </si>
   <si>
+    <t>0,31.5</t>
+  </si>
+  <si>
+    <t>323,57</t>
+  </si>
+  <si>
     <t>role1.hit4</t>
   </si>
   <si>
@@ -251,6 +281,12 @@
     <t>WukongAttack4</t>
   </si>
   <si>
+    <t>38.5,38</t>
+  </si>
+  <si>
+    <t>273,74</t>
+  </si>
+  <si>
     <t>monster1.hit1</t>
   </si>
   <si>
@@ -263,13 +299,19 @@
     <t>0,0</t>
   </si>
   <si>
-    <t>-3,-6</t>
+    <t>3,-6</t>
   </si>
   <si>
     <t>None</t>
   </si>
   <si>
     <t>HuaguoshanMonkey</t>
+  </si>
+  <si>
+    <t>24,-10</t>
+  </si>
+  <si>
+    <t>50,50</t>
   </si>
 </sst>
 </file>
@@ -883,8 +925,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1231,467 +1276,521 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:T10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="8.54545454545454" customWidth="1"/>
-    <col min="2" max="2" width="7.54545454545455" customWidth="1"/>
-    <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="4" max="4" width="10.6363636363636" customWidth="1"/>
-    <col min="5" max="5" width="23" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="26.8181818181818" customWidth="1"/>
-    <col min="8" max="8" width="29.8181818181818" customWidth="1"/>
-    <col min="9" max="9" width="19.0909090909091" customWidth="1"/>
-    <col min="10" max="10" width="19.6363636363636" customWidth="1"/>
-    <col min="11" max="12" width="32" customWidth="1"/>
-    <col min="13" max="13" width="53.3636363636364" customWidth="1"/>
-    <col min="14" max="14" width="34.2727272727273" customWidth="1"/>
-    <col min="15" max="15" width="33.1818181818182" customWidth="1"/>
-    <col min="16" max="16" width="27" customWidth="1"/>
+    <col min="1" max="1" width="8.54545454545454" style="1" customWidth="1"/>
+    <col min="2" max="2" width="7.54545454545455" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.8181818181818" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.6363636363636" style="1" customWidth="1"/>
+    <col min="5" max="5" width="23" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.1818181818182" style="1" customWidth="1"/>
+    <col min="8" max="8" width="11.4545454545455" style="1" customWidth="1"/>
+    <col min="9" max="9" width="19.0909090909091" style="1" customWidth="1"/>
+    <col min="10" max="10" width="19.6363636363636" style="1" customWidth="1"/>
+    <col min="11" max="11" width="12.2727272727273" style="1" customWidth="1"/>
+    <col min="12" max="12" width="13.2727272727273" style="1" customWidth="1"/>
+    <col min="13" max="13" width="13.8181818181818" style="1" customWidth="1"/>
+    <col min="14" max="14" width="19" style="1" customWidth="1"/>
+    <col min="15" max="15" width="19.6363636363636" style="1" customWidth="1"/>
+    <col min="16" max="16" width="21.2727272727273" style="1" customWidth="1"/>
+    <col min="17" max="17" width="13.6363636363636" style="1" customWidth="1"/>
+    <col min="18" max="18" width="11.0909090909091" style="1" customWidth="1"/>
+    <col min="19" max="19" width="13.8181818181818" style="1" customWidth="1"/>
+    <col min="20" max="20" width="17.4545454545455" style="1" customWidth="1"/>
+    <col min="21" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
-      <c r="A1" t="s">
+    <row r="1" ht="15" customHeight="1" spans="1:20">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="2" spans="1:18">
-      <c r="A2" t="s">
+    <row r="2" spans="1:20">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:18">
-      <c r="A3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
+    <row r="3" spans="1:20">
+      <c r="A3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="B3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="C3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J3" t="s">
+      <c r="D3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="K3" t="s">
+      <c r="I3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="L3" t="s">
-        <v>19</v>
-      </c>
-      <c r="M3" t="s">
-        <v>24</v>
-      </c>
-      <c r="N3" t="s">
+      <c r="K3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="O3" t="s">
-        <v>25</v>
-      </c>
-      <c r="P3" t="s">
+      <c r="L3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Q3" t="s">
-        <v>19</v>
-      </c>
-      <c r="R3" t="s">
-        <v>19</v>
+      <c r="N3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:18">
-      <c r="A4" t="s">
-        <v>27</v>
+    <row r="4" spans="1:20">
+      <c r="A4" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:18">
-      <c r="A5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" t="s">
+    <row r="5" ht="112" spans="1:20">
+      <c r="A5" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D5" t="s">
+      <c r="B5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E5" t="s">
+      <c r="C5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F5" t="s">
+      <c r="D5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G5" t="s">
+      <c r="E5" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H5" t="s">
+      <c r="F5" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="I5" t="s">
+      <c r="G5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="J5" t="s">
+      <c r="H5" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="K5" t="s">
+      <c r="I5" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="L5" t="s">
+      <c r="J5" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="M5" t="s">
+      <c r="K5" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="N5" t="s">
+      <c r="L5" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="O5" t="s">
+      <c r="M5" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="P5" t="s">
+      <c r="N5" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="O5" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="R5" t="s">
+      <c r="P5" s="1" t="s">
         <v>45</v>
       </c>
+      <c r="Q5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>49</v>
+      </c>
     </row>
-    <row r="6" spans="1:18">
-      <c r="B6">
+    <row r="6" spans="1:20">
+      <c r="B6" s="1">
         <v>1001</v>
       </c>
-      <c r="C6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D6" t="s">
-        <v>47</v>
-      </c>
-      <c r="E6" t="s">
-        <v>48</v>
-      </c>
-      <c r="F6" t="s">
-        <v>49</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="C6" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="H6">
+      <c r="D6" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H6" s="1">
         <v>0</v>
       </c>
-      <c r="I6" t="s">
-        <v>51</v>
-      </c>
-      <c r="J6" t="s">
-        <v>52</v>
-      </c>
-      <c r="K6" t="s">
+      <c r="I6" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="L6" s="1">
+        <v>0</v>
+      </c>
+      <c r="M6" s="1">
+        <v>0.35</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>0</v>
+      </c>
+      <c r="R6" s="1">
+        <v>0</v>
+      </c>
+      <c r="S6" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="T6" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" ht="28" spans="1:20">
+      <c r="B7" s="1">
+        <v>1002</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="L7" s="1">
+        <v>0</v>
+      </c>
+      <c r="M7" s="1">
+        <v>0.35</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>1</v>
+      </c>
+      <c r="R7" s="1">
+        <v>0</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20">
+      <c r="B8" s="1">
+        <v>1003</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="L8" s="1">
+        <v>0</v>
+      </c>
+      <c r="M8" s="1">
+        <v>0.35</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>2</v>
+      </c>
+      <c r="R8" s="1">
+        <v>0</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20">
+      <c r="B9" s="1">
+        <v>1004</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="L9" s="1">
+        <v>0</v>
+      </c>
+      <c r="M9" s="1">
+        <v>0.35</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>3</v>
+      </c>
+      <c r="R9" s="1">
+        <v>0</v>
+      </c>
+      <c r="S9" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T9" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20">
+      <c r="B10" s="1">
+        <v>2001</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="L6">
+      <c r="G10" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H10" s="1">
+        <v>10</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="L10" s="1">
+        <v>10</v>
+      </c>
+      <c r="M10" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q10" s="1">
         <v>0</v>
       </c>
-      <c r="M6">
-        <v>0.35</v>
-      </c>
-      <c r="N6" t="s">
-        <v>54</v>
-      </c>
-      <c r="O6" t="s">
-        <v>55</v>
-      </c>
-      <c r="P6" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18">
-      <c r="B7">
-        <v>1002</v>
-      </c>
-      <c r="C7" t="s">
-        <v>57</v>
-      </c>
-      <c r="D7" t="s">
-        <v>58</v>
-      </c>
-      <c r="E7" t="s">
-        <v>59</v>
-      </c>
-      <c r="F7" t="s">
-        <v>60</v>
-      </c>
-      <c r="G7" t="s">
-        <v>61</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7" t="s">
-        <v>51</v>
-      </c>
-      <c r="J7" t="s">
-        <v>52</v>
-      </c>
-      <c r="K7" t="s">
-        <v>53</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0.35</v>
-      </c>
-      <c r="N7" t="s">
-        <v>62</v>
-      </c>
-      <c r="O7" t="s">
-        <v>55</v>
-      </c>
-      <c r="P7" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q7">
-        <v>1</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18">
-      <c r="B8">
-        <v>1003</v>
-      </c>
-      <c r="C8" t="s">
-        <v>63</v>
-      </c>
-      <c r="D8" t="s">
-        <v>64</v>
-      </c>
-      <c r="E8" t="s">
-        <v>65</v>
-      </c>
-      <c r="F8" t="s">
-        <v>66</v>
-      </c>
-      <c r="G8" t="s">
-        <v>50</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8" t="s">
-        <v>51</v>
-      </c>
-      <c r="J8" t="s">
-        <v>52</v>
-      </c>
-      <c r="K8" t="s">
-        <v>53</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0.35</v>
-      </c>
-      <c r="N8" t="s">
-        <v>54</v>
-      </c>
-      <c r="O8" t="s">
-        <v>55</v>
-      </c>
-      <c r="P8" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q8">
-        <v>2</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18">
-      <c r="B9">
-        <v>1004</v>
-      </c>
-      <c r="C9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D9" t="s">
-        <v>68</v>
-      </c>
-      <c r="E9" t="s">
-        <v>69</v>
-      </c>
-      <c r="F9" t="s">
-        <v>70</v>
-      </c>
-      <c r="G9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9" t="s">
-        <v>51</v>
-      </c>
-      <c r="J9" t="s">
-        <v>72</v>
-      </c>
-      <c r="K9" t="s">
-        <v>53</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0.35</v>
-      </c>
-      <c r="N9" t="s">
-        <v>73</v>
-      </c>
-      <c r="O9" t="s">
-        <v>55</v>
-      </c>
-      <c r="P9" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q9">
-        <v>3</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18">
-      <c r="B10">
-        <v>2001</v>
-      </c>
-      <c r="C10" t="s">
-        <v>74</v>
-      </c>
-      <c r="D10" t="s">
-        <v>75</v>
-      </c>
-      <c r="E10" t="s">
-        <v>76</v>
-      </c>
-      <c r="F10" t="s">
-        <v>49</v>
-      </c>
-      <c r="G10" t="s">
-        <v>77</v>
-      </c>
-      <c r="H10">
-        <v>10</v>
-      </c>
-      <c r="I10" t="s">
-        <v>51</v>
-      </c>
-      <c r="J10" t="s">
-        <v>78</v>
-      </c>
-      <c r="K10" t="s">
-        <v>77</v>
-      </c>
-      <c r="L10">
-        <v>10</v>
-      </c>
-      <c r="M10">
-        <v>0.6</v>
-      </c>
-      <c r="N10" t="s">
-        <v>79</v>
-      </c>
-      <c r="O10" t="s">
-        <v>79</v>
-      </c>
-      <c r="P10" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
-      <c r="R10">
+      <c r="R10" s="1">
         <v>100</v>
+      </c>
+      <c r="S10" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="T10" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/AttackConfig.xlsx
+++ b/Configs/GameConfig/Datas/AttackConfig.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="25600" windowHeight="10480" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1034,7 +1034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T10"/>
+  <dimension ref="A1:U10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="8.54545454545454" customWidth="1" style="1" min="1" max="1"/>
@@ -1146,9 +1146,26 @@
           <t>AiWeight</t>
         </is>
       </c>
-      <c r="R1" s="1" t="n"/>
-      <c r="S1" s="1" t="n"/>
-      <c r="T1" s="1" t="n"/>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>AiPriority</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>AiRange</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>AiCooldown</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>AiInitCooldown</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -1243,9 +1260,26 @@
           <t>int</t>
         </is>
       </c>
-      <c r="R3" s="1" t="n"/>
-      <c r="S3" s="1" t="n"/>
-      <c r="T3" s="1" t="n"/>
+      <c r="R3" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="S3" s="1" t="inlineStr">
+        <is>
+          <t>vector2</t>
+        </is>
+      </c>
+      <c r="T3" s="1" t="inlineStr">
+        <is>
+          <t>vector2</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>vector2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1340,9 +1374,26 @@
           <t>AI 选招权重(怪物 AI 用;英雄普攻填 0)</t>
         </is>
       </c>
-      <c r="R5" s="1" t="n"/>
-      <c r="S5" s="1" t="n"/>
-      <c r="T5" s="1" t="n"/>
+      <c r="R5" s="1" t="inlineStr">
+        <is>
+          <t>AI 优先级:0=普攻池(按攻击欲望掷骰+权重抽);&gt;0=技能(冷却就绪且距离满足即放,大者优先,追击途中也会放)</t>
+        </is>
+      </c>
+      <c r="S5" s="1" t="inlineStr">
+        <is>
+          <t>AI 释放距离 px(X=最小,Y=最大;只比水平距离,写法 0,45)</t>
+        </is>
+      </c>
+      <c r="T5" s="1" t="inlineStr">
+        <is>
+          <t>AI 释放后冷却秒(X=下限,Y=上限随机;普攻池填 0,0)</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>AI 出生时初始冷却秒(X=下限,Y=上限;旧 _ready 里 Skill_N_CD=randi_range)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="n">
@@ -1415,6 +1466,24 @@
       <c r="Q6" t="n">
         <v>0</v>
       </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="B7" t="n">
@@ -1487,6 +1556,24 @@
       <c r="Q7" t="n">
         <v>0</v>
       </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="B8" t="n">
@@ -1559,6 +1646,24 @@
       <c r="Q8" t="n">
         <v>0</v>
       </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="B9" t="n">
@@ -1631,6 +1736,24 @@
       <c r="Q9" t="n">
         <v>0</v>
       </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="B10" t="n">
@@ -1702,6 +1825,24 @@
       </c>
       <c r="Q10" t="n">
         <v>100</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0,70</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/AttackConfig.xlsx
+++ b/Configs/GameConfig/Datas/AttackConfig.xlsx
@@ -1034,7 +1034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="8.54545454545454" customWidth="1" style="1" min="1" max="1"/>
@@ -1877,6 +1877,192 @@
         <v>0.3</v>
       </c>
     </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>2002</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>monster2.hit1</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>妖猴扑击</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>追击途中发起的攻击(旧 RunHit)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>attack_1</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>20</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>4,-9</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>15</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>DemonMonkey</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>100</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1.5,1.5</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>2003</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>monster2.hit1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>妖猴普攻</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>站定后的普通攻击</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>attack_1</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>20</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>4,-9</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>15</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>DemonMonkey</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>100</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/AttackConfig.xlsx
+++ b/Configs/GameConfig/Datas/AttackConfig.xlsx
@@ -1219,7 +1219,7 @@
       </c>
       <c r="H3" s="1" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>vector2</t>
         </is>
       </c>
       <c r="I3" s="1" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="H5" s="1" t="inlineStr">
         <is>
-          <t>固定攻击力(不与属性挂钩)</t>
+          <t>额外威力范围；英雄普攻 0,4 对应官方随机攻击，怪物填固定值范围</t>
         </is>
       </c>
       <c r="I5" s="1" t="inlineStr">
@@ -1438,11 +1438,13 @@
       </c>
       <c r="G6" s="1" t="inlineStr">
         <is>
-          <t>1,1.2</t>
-        </is>
-      </c>
-      <c r="H6" s="1" t="n">
-        <v>0</v>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="H6" s="1" t="inlineStr">
+        <is>
+          <t>0,4</t>
+        </is>
       </c>
       <c r="I6" s="1" t="inlineStr">
         <is>
@@ -1531,11 +1533,13 @@
       </c>
       <c r="G7" s="1" t="inlineStr">
         <is>
-          <t>0.9,1.1</t>
-        </is>
-      </c>
-      <c r="H7" s="1" t="n">
-        <v>0</v>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="H7" s="1" t="inlineStr">
+        <is>
+          <t>0,4</t>
+        </is>
       </c>
       <c r="I7" s="1" t="inlineStr">
         <is>
@@ -1624,11 +1628,13 @@
       </c>
       <c r="G8" s="1" t="inlineStr">
         <is>
-          <t>1,1.2</t>
-        </is>
-      </c>
-      <c r="H8" s="1" t="n">
-        <v>0</v>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="H8" s="1" t="inlineStr">
+        <is>
+          <t>0,4</t>
+        </is>
       </c>
       <c r="I8" s="1" t="inlineStr">
         <is>
@@ -1717,11 +1723,13 @@
       </c>
       <c r="G9" s="1" t="inlineStr">
         <is>
-          <t>1.2,1.4</t>
-        </is>
-      </c>
-      <c r="H9" s="1" t="n">
-        <v>0</v>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="H9" s="1" t="inlineStr">
+        <is>
+          <t>0,4</t>
+        </is>
       </c>
       <c r="I9" s="1" t="inlineStr">
         <is>
@@ -1813,8 +1821,10 @@
           <t>0,0</t>
         </is>
       </c>
-      <c r="H10" s="1" t="n">
-        <v>10</v>
+      <c r="H10" s="1" t="inlineStr">
+        <is>
+          <t>5,5</t>
+        </is>
       </c>
       <c r="I10" s="1" t="inlineStr">
         <is>
@@ -1823,7 +1833,7 @@
       </c>
       <c r="J10" s="1" t="inlineStr">
         <is>
-          <t>3,-6</t>
+          <t>2,-5</t>
         </is>
       </c>
       <c r="K10" s="1" t="inlineStr">
@@ -1832,7 +1842,7 @@
         </is>
       </c>
       <c r="L10" s="1" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="M10" s="1" t="inlineStr">
         <is>
@@ -1870,7 +1880,7 @@
       </c>
       <c r="U10" s="1" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0.5,1.0</t>
         </is>
       </c>
       <c r="V10" s="1" t="n">
@@ -1879,7 +1889,7 @@
     </row>
     <row r="11">
       <c r="B11" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1888,12 +1898,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>妖猴扑击</t>
+          <t>妖猴普攻</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>追击途中发起的攻击(旧 RunHit)</t>
+          <t>站定后的普通攻击</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1906,8 +1916,10 @@
           <t>0,0</t>
         </is>
       </c>
-      <c r="H11" t="n">
-        <v>20</v>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>12,12</t>
+        </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1916,7 +1928,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4,-9</t>
+          <t>6,-5</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1925,7 +1937,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1949,7 +1961,7 @@
         <v>100</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1958,12 +1970,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1.5,1.5</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0.5,1.0</t>
         </is>
       </c>
       <c r="V11" t="n">
@@ -1972,21 +1984,21 @@
     </row>
     <row r="12">
       <c r="B12" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>monster2.hit1</t>
+          <t>official.Monster3.hit1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>妖猴普攻</t>
+          <t>大猩猩重拳</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>站定后的普通攻击</t>
+          <t>前摇抬拳后打出，结束后收招</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1999,8 +2011,10 @@
           <t>0,0</t>
         </is>
       </c>
-      <c r="H12" t="n">
-        <v>20</v>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>20,20</t>
+        </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -2009,7 +2023,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4,-9</t>
+          <t>6,-5</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -2018,7 +2032,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -2032,7 +2046,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>DemonMonkey</t>
+          <t>Gorilla</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -2056,11 +2070,11 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0.5,1.0</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/AttackConfig.xlsx
+++ b/Configs/GameConfig/Datas/AttackConfig.xlsx
@@ -1034,7 +1034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:U12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="8.54545454545454" customWidth="1" style="1" min="1" max="1"/>
@@ -1115,60 +1115,55 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>WsGain</t>
+          <t>HitProtect</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>HitProtect</t>
+          <t>SoundId</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>SoundId</t>
+          <t>HitSoundId</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>HitSoundId</t>
+          <t>OwnerId</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>OwnerId</t>
+          <t>ComboIndex</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>ComboIndex</t>
+          <t>AiWeight</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>AiWeight</t>
+          <t>AiPriority</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>AiPriority</t>
+          <t>AiRange</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>AiRange</t>
+          <t>AiCooldown</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>AiCooldown</t>
+          <t>AiInitCooldown</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>AiInitCooldown</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>AiRecovery</t>
         </is>
@@ -1234,29 +1229,29 @@
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>vector2i</t>
+          <t>int</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
+          <t>Sound.SoundId</t>
+        </is>
+      </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Sound.SoundId</t>
+        </is>
+      </c>
+      <c r="N3" s="1" t="inlineStr">
+        <is>
+          <t>Entity.EntityId</t>
+        </is>
+      </c>
+      <c r="O3" s="1" t="inlineStr">
+        <is>
           <t>int</t>
         </is>
       </c>
-      <c r="M3" s="1" t="inlineStr">
-        <is>
-          <t>Sound.SoundId</t>
-        </is>
-      </c>
-      <c r="N3" s="1" t="inlineStr">
-        <is>
-          <t>Sound.SoundId</t>
-        </is>
-      </c>
-      <c r="O3" s="1" t="inlineStr">
-        <is>
-          <t>Entity.EntityId</t>
-        </is>
-      </c>
       <c r="P3" s="1" t="inlineStr">
         <is>
           <t>int</t>
@@ -1269,7 +1264,7 @@
       </c>
       <c r="R3" s="1" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>vector2</t>
         </is>
       </c>
       <c r="S3" s="1" t="inlineStr">
@@ -1283,11 +1278,6 @@
         </is>
       </c>
       <c r="U3" s="1" t="inlineStr">
-        <is>
-          <t>vector2</t>
-        </is>
-      </c>
-      <c r="V3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
@@ -1353,60 +1343,55 @@
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>命中获得无双值范围(旧 WSValue,X=下限,Y=上限,写法 3,5)</t>
+          <t>受击保护累计值(旧 HitProtect)</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
-          <t>受击保护累计值(旧 HitProtect)</t>
+          <t>起手音效(SoundConfig;None=无)</t>
         </is>
       </c>
       <c r="M5" s="1" t="inlineStr">
         <is>
-          <t>起手音效(SoundConfig;None=无)</t>
+          <t>命中音效(打中目标时播,None=无;旧项目按攻击者选音)</t>
         </is>
       </c>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>命中音效(打中目标时播,None=无;旧项目按攻击者选音)</t>
+          <t>这招属于谁(None=通用招,将来多主体共享用)</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>这招属于谁(None=通用招,将来多主体共享用)</t>
+          <t>连段第几段(0起;同一 OwnerId 内连续,越大越靠后)</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr">
         <is>
-          <t>连段第几段(0起;同一 OwnerId 内连续,越大越靠后)</t>
+          <t>AI 选招权重(怪物 AI 用;英雄普攻填 0)</t>
         </is>
       </c>
       <c r="Q5" s="1" t="inlineStr">
         <is>
-          <t>AI 选招权重(怪物 AI 用;英雄普攻填 0)</t>
+          <t>AI 优先级:0=普攻(按攻击欲望掷骰+权重抽);&gt;0=优先招(冷却就绪且够得着即先放,大者优先,接近途中也会放)</t>
         </is>
       </c>
       <c r="R5" s="1" t="inlineStr">
         <is>
-          <t>AI 优先级:0=普攻(按攻击欲望掷骰+权重抽);&gt;0=优先招(冷却就绪且够得着即先放,大者优先,接近途中也会放)</t>
+          <t>AI 释放距离 px(仅远程/无身体判定盒的招式;X=最小,Y=最大,只比水平距离;0,0=按攻击动画判定盒推导)</t>
         </is>
       </c>
       <c r="S5" s="1" t="inlineStr">
         <is>
-          <t>AI 释放距离 px(仅远程/无身体判定盒的招式;X=最小,Y=最大,只比水平距离;0,0=按攻击动画判定盒推导)</t>
+          <t>AI 释放后冷却秒(X=下限,Y=上限随机;普攻池填 0,0)</t>
         </is>
       </c>
       <c r="T5" s="1" t="inlineStr">
         <is>
-          <t>AI 释放后冷却秒(X=下限,Y=上限随机;普攻池填 0,0)</t>
+          <t>AI 出生时初始冷却秒(X=下限,Y=上限;旧 _ready 里 Skill_N_CD=randi_range)</t>
         </is>
       </c>
       <c r="U5" s="1" t="inlineStr">
-        <is>
-          <t>AI 出生时初始冷却秒(X=下限,Y=上限;旧 _ready 里 Skill_N_CD=randi_range)</t>
-        </is>
-      </c>
-      <c r="V5" s="1" t="inlineStr">
         <is>
           <t>AI 收招硬直秒:收招后原地不动、不转身、不出招(英雄填 0)</t>
         </is>
@@ -1456,37 +1441,37 @@
           <t>2,0</t>
         </is>
       </c>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>3,5</t>
-        </is>
-      </c>
-      <c r="L6" s="1" t="n">
-        <v>0</v>
+      <c r="K6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1" t="inlineStr">
+        <is>
+          <t>WukongAttack1And3</t>
+        </is>
       </c>
       <c r="M6" s="1" t="inlineStr">
         <is>
-          <t>WukongAttack1And3</t>
+          <t>WukongImpact</t>
         </is>
       </c>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>WukongImpact</t>
-        </is>
-      </c>
-      <c r="O6" s="1" t="inlineStr">
-        <is>
           <t>Wukong</t>
         </is>
       </c>
+      <c r="O6" s="1" t="n">
+        <v>0</v>
+      </c>
       <c r="P6" s="1" t="n">
         <v>0</v>
       </c>
       <c r="Q6" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R6" s="1" t="n">
-        <v>0</v>
+      <c r="R6" s="1" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
       </c>
       <c r="S6" s="1" t="inlineStr">
         <is>
@@ -1498,12 +1483,7 @@
           <t>0,0</t>
         </is>
       </c>
-      <c r="U6" s="1" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="V6" s="1" t="n">
+      <c r="U6" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1551,37 +1531,37 @@
           <t>2,0</t>
         </is>
       </c>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>3,5</t>
-        </is>
-      </c>
-      <c r="L7" s="1" t="n">
-        <v>0</v>
+      <c r="K7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1" t="inlineStr">
+        <is>
+          <t>WukongAttack2</t>
+        </is>
       </c>
       <c r="M7" s="1" t="inlineStr">
         <is>
-          <t>WukongAttack2</t>
+          <t>WukongImpact</t>
         </is>
       </c>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>WukongImpact</t>
-        </is>
-      </c>
-      <c r="O7" s="1" t="inlineStr">
-        <is>
           <t>Wukong</t>
         </is>
       </c>
+      <c r="O7" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="P7" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R7" s="1" t="n">
-        <v>0</v>
+      <c r="R7" s="1" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
       </c>
       <c r="S7" s="1" t="inlineStr">
         <is>
@@ -1593,12 +1573,7 @@
           <t>0,0</t>
         </is>
       </c>
-      <c r="U7" s="1" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="V7" s="1" t="n">
+      <c r="U7" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1646,37 +1621,37 @@
           <t>2,0</t>
         </is>
       </c>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>3,5</t>
-        </is>
-      </c>
-      <c r="L8" s="1" t="n">
-        <v>0</v>
+      <c r="K8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="1" t="inlineStr">
+        <is>
+          <t>WukongAttack1And3</t>
+        </is>
       </c>
       <c r="M8" s="1" t="inlineStr">
         <is>
-          <t>WukongAttack1And3</t>
+          <t>WukongImpact</t>
         </is>
       </c>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>WukongImpact</t>
-        </is>
-      </c>
-      <c r="O8" s="1" t="inlineStr">
-        <is>
           <t>Wukong</t>
         </is>
       </c>
+      <c r="O8" s="1" t="n">
+        <v>2</v>
+      </c>
       <c r="P8" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R8" s="1" t="n">
-        <v>0</v>
+      <c r="R8" s="1" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
       </c>
       <c r="S8" s="1" t="inlineStr">
         <is>
@@ -1688,12 +1663,7 @@
           <t>0,0</t>
         </is>
       </c>
-      <c r="U8" s="1" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="V8" s="1" t="n">
+      <c r="U8" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1741,37 +1711,37 @@
           <t>6,-5</t>
         </is>
       </c>
-      <c r="K9" s="1" t="inlineStr">
-        <is>
-          <t>3,5</t>
-        </is>
-      </c>
-      <c r="L9" s="1" t="n">
-        <v>0</v>
+      <c r="K9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="1" t="inlineStr">
+        <is>
+          <t>WukongAttack4</t>
+        </is>
       </c>
       <c r="M9" s="1" t="inlineStr">
         <is>
-          <t>WukongAttack4</t>
+          <t>WukongImpact</t>
         </is>
       </c>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>WukongImpact</t>
-        </is>
-      </c>
-      <c r="O9" s="1" t="inlineStr">
-        <is>
           <t>Wukong</t>
         </is>
       </c>
+      <c r="O9" s="1" t="n">
+        <v>3</v>
+      </c>
       <c r="P9" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R9" s="1" t="n">
-        <v>0</v>
+      <c r="R9" s="1" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
       </c>
       <c r="S9" s="1" t="inlineStr">
         <is>
@@ -1783,12 +1753,7 @@
           <t>0,0</t>
         </is>
       </c>
-      <c r="U9" s="1" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="V9" s="1" t="n">
+      <c r="U9" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1836,38 +1801,38 @@
           <t>2,-5</t>
         </is>
       </c>
-      <c r="K10" s="1" t="inlineStr">
+      <c r="K10" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="L10" s="1" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M10" s="1" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N10" s="1" t="inlineStr">
+        <is>
+          <t>HuaguoshanMonkey</t>
+        </is>
+      </c>
+      <c r="O10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" s="1" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="L10" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="M10" s="1" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="N10" s="1" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O10" s="1" t="inlineStr">
-        <is>
-          <t>HuaguoshanMonkey</t>
-        </is>
-      </c>
-      <c r="P10" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="R10" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="S10" s="1" t="inlineStr">
         <is>
           <t>0,0</t>
@@ -1875,15 +1840,10 @@
       </c>
       <c r="T10" s="1" t="inlineStr">
         <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="U10" s="1" t="inlineStr">
-        <is>
           <t>0.5,1.0</t>
         </is>
       </c>
-      <c r="V10" s="1" t="n">
+      <c r="U10" s="1" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -1931,38 +1891,38 @@
           <t>6,-5</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K11" t="n">
+        <v>4</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>DemonMonkey</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="L11" t="n">
-        <v>4</v>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>DemonMonkey</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>100</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
       <c r="S11" t="inlineStr">
         <is>
           <t>0,0</t>
@@ -1970,15 +1930,10 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
           <t>0.5,1.0</t>
         </is>
       </c>
-      <c r="V11" t="n">
+      <c r="U11" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -2026,38 +1981,38 @@
           <t>6,-5</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Gorilla</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="L12" t="n">
-        <v>4</v>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Gorilla</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>100</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
           <t>0,0</t>
@@ -2065,15 +2020,10 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
           <t>0.5,1.0</t>
         </is>
       </c>
-      <c r="V12" t="n">
+      <c r="U12" t="n">
         <v>0.6</v>
       </c>
     </row>

--- a/Configs/GameConfig/Datas/AttackConfig.xlsx
+++ b/Configs/GameConfig/Datas/AttackConfig.xlsx
@@ -1,177 +1,154 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="25600" windowHeight="12080" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5c569d3a696f4713"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fonts count="20">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u val="single"/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u val="single"/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="18"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C6500"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="0"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -179,187 +156,156 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39998"/>
       </patternFill>
     </fill>
   </fills>
@@ -400,7 +346,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4" tint="0.49998"/>
       </bottom>
       <diagonal/>
     </border>
@@ -618,63 +564,62 @@
     </xf>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规" xfId="0"/>
+    <cellStyle name="千位分隔" xfId="1"/>
+    <cellStyle name="货币" xfId="2"/>
+    <cellStyle name="百分比" xfId="3"/>
+    <cellStyle name="千位分隔[0]" xfId="4"/>
+    <cellStyle name="货币[0]" xfId="5"/>
+    <cellStyle name="超链接" xfId="6"/>
+    <cellStyle name="已访问的超链接" xfId="7"/>
+    <cellStyle name="注释" xfId="8"/>
+    <cellStyle name="警告文本" xfId="9"/>
+    <cellStyle name="标题" xfId="10"/>
+    <cellStyle name="解释性文本" xfId="11"/>
+    <cellStyle name="标题 1" xfId="12"/>
+    <cellStyle name="标题 2" xfId="13"/>
+    <cellStyle name="标题 3" xfId="14"/>
+    <cellStyle name="标题 4" xfId="15"/>
+    <cellStyle name="输入" xfId="16"/>
+    <cellStyle name="输出" xfId="17"/>
+    <cellStyle name="计算" xfId="18"/>
+    <cellStyle name="检查单元格" xfId="19"/>
+    <cellStyle name="链接单元格" xfId="20"/>
+    <cellStyle name="汇总" xfId="21"/>
+    <cellStyle name="好" xfId="22"/>
+    <cellStyle name="差" xfId="23"/>
+    <cellStyle name="适中" xfId="24"/>
+    <cellStyle name="强调文字颜色 1" xfId="25"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28"/>
+    <cellStyle name="强调文字颜色 2" xfId="29"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32"/>
+    <cellStyle name="强调文字颜色 3" xfId="33"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36"/>
+    <cellStyle name="强调文字颜色 4" xfId="37"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40"/>
+    <cellStyle name="强调文字颜色 5" xfId="41"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44"/>
+    <cellStyle name="强调文字颜色 6" xfId="45"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -910,7 +855,7 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -919,13 +864,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -959,17 +904,6 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -1024,376 +958,370 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:U12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col width="8.54545454545454" customWidth="1" style="1" min="1" max="1"/>
-    <col width="7.54545454545455" customWidth="1" style="1" min="2" max="2"/>
-    <col width="15.8181818181818" customWidth="1" style="1" min="3" max="3"/>
-    <col width="10.6363636363636" customWidth="1" style="1" min="4" max="4"/>
-    <col width="23" customWidth="1" style="1" min="5" max="5"/>
-    <col width="14" customWidth="1" style="1" min="6" max="6"/>
-    <col width="12.1818181818182" customWidth="1" style="1" min="7" max="7"/>
-    <col width="11.4545454545455" customWidth="1" style="1" min="8" max="8"/>
-    <col width="19.0909090909091" customWidth="1" style="1" min="9" max="9"/>
-    <col width="19.6363636363636" customWidth="1" style="1" min="10" max="10"/>
-    <col width="12.2727272727273" customWidth="1" style="1" min="11" max="11"/>
-    <col width="13.2727272727273" customWidth="1" style="1" min="12" max="12"/>
-    <col width="13.8181818181818" customWidth="1" style="1" min="13" max="13"/>
-    <col width="19" customWidth="1" style="1" min="14" max="14"/>
-    <col width="19.6363636363636" customWidth="1" style="1" min="15" max="15"/>
-    <col width="21.2727272727273" customWidth="1" style="1" min="16" max="16"/>
-    <col width="13.6363636363636" customWidth="1" style="1" min="17" max="17"/>
-    <col width="11.0909090909091" customWidth="1" style="1" min="18" max="18"/>
-    <col width="13.8181818181818" customWidth="1" style="1" min="19" max="19"/>
-    <col width="17.4545454545455" customWidth="1" style="1" min="20" max="20"/>
-    <col width="17.1818181818182" customWidth="1" style="1" min="21" max="21"/>
-    <col width="14.6363636363636" customWidth="1" style="1" min="22" max="22"/>
-    <col width="9" customWidth="1" style="1" min="23" max="16384"/>
+    <col min="1" max="1" width="8.545454978942871" style="1" customWidth="1"/>
+    <col min="2" max="2" width="7.545454502105713" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.818181991577148" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.636363983154297" style="1" customWidth="1"/>
+    <col min="5" max="5" width="23" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.181818008422852" style="1" customWidth="1"/>
+    <col min="8" max="8" width="11.454545021057129" style="1" customWidth="1"/>
+    <col min="9" max="9" width="19.090909957885742" style="1" customWidth="1"/>
+    <col min="10" max="10" width="19.636363983154297" style="1" customWidth="1"/>
+    <col min="11" max="11" width="12.272727012634277" style="1" customWidth="1"/>
+    <col min="12" max="12" width="13.272727012634277" style="1" customWidth="1"/>
+    <col min="13" max="13" width="13.818181991577148" style="1" customWidth="1"/>
+    <col min="14" max="14" width="19" style="1" customWidth="1"/>
+    <col min="15" max="15" width="19.636363983154297" style="1" customWidth="1"/>
+    <col min="16" max="16" width="21.272727966308594" style="1" customWidth="1"/>
+    <col min="17" max="17" width="13.636363983154297" style="1" customWidth="1"/>
+    <col min="18" max="18" width="11.090909004211426" style="1" customWidth="1"/>
+    <col min="19" max="19" width="13.818181991577148" style="1" customWidth="1"/>
+    <col min="20" max="20" width="17.454545974731445" style="1" customWidth="1"/>
+    <col min="21" max="21" width="17.18181800842285" style="1" customWidth="1"/>
+    <col min="22" max="22" width="14.636363983154297" style="1" customWidth="1"/>
+    <col min="23" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>##var</t>
+          <t xml:space="preserve">##var</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t xml:space="preserve">Id</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>LegacyId</t>
+          <t xml:space="preserve">LegacyId</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>NameCn</t>
+          <t xml:space="preserve">NameCn</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Desc</t>
+          <t xml:space="preserve">Desc</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Animation</t>
+          <t xml:space="preserve">Animation</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>PowerScale</t>
+          <t xml:space="preserve">PowerScale</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>FlatPower</t>
+          <t xml:space="preserve">FlatPower</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>DamageKind</t>
+          <t xml:space="preserve">DamageKind</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Knockback</t>
+          <t xml:space="preserve">Knockback</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>HitProtect</t>
+          <t xml:space="preserve">HitProtect</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>SoundId</t>
+          <t xml:space="preserve">SoundId</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>HitSoundId</t>
+          <t xml:space="preserve">HitSoundId</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>OwnerId</t>
+          <t xml:space="preserve">OwnerId</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>ComboIndex</t>
+          <t xml:space="preserve">ComboIndex</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>AiWeight</t>
+          <t xml:space="preserve">AiWeight</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>AiPriority</t>
+          <t xml:space="preserve">AiPriority</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>AiRange</t>
+          <t xml:space="preserve">AiRange</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>AiCooldown</t>
+          <t xml:space="preserve">AiCooldown</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>AiInitCooldown</t>
+          <t xml:space="preserve">AiInitCooldown</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>AiRecovery</t>
+          <t xml:space="preserve">AiRecovery</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>##var</t>
+          <t xml:space="preserve">##var</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>##type</t>
+          <t xml:space="preserve">##type</t>
         </is>
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>int</t>
+          <t xml:space="preserve">int</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>string</t>
+          <t xml:space="preserve">string</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>string</t>
+          <t xml:space="preserve">string</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t>string</t>
+          <t xml:space="preserve">string</t>
         </is>
       </c>
       <c r="F3" s="1" t="inlineStr">
         <is>
-          <t>string</t>
+          <t xml:space="preserve">string</t>
         </is>
       </c>
       <c r="G3" s="1" t="inlineStr">
         <is>
-          <t>vector2</t>
+          <t xml:space="preserve">vector2</t>
         </is>
       </c>
       <c r="H3" s="1" t="inlineStr">
         <is>
-          <t>vector2</t>
+          <t xml:space="preserve">vector2</t>
         </is>
       </c>
       <c r="I3" s="1" t="inlineStr">
         <is>
-          <t>Battle.DamageKind</t>
+          <t xml:space="preserve">Battle.DamageKind</t>
         </is>
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>vector2</t>
+          <t xml:space="preserve">vector2</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>int</t>
+          <t xml:space="preserve">int</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
-          <t>Sound.SoundId</t>
+          <t xml:space="preserve">Sound.SoundId</t>
         </is>
       </c>
       <c r="M3" s="1" t="inlineStr">
         <is>
-          <t>Sound.SoundId</t>
+          <t xml:space="preserve">Sound.SoundId</t>
         </is>
       </c>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>Entity.EntityId</t>
+          <t xml:space="preserve">Entity.EntityId</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>int</t>
+          <t xml:space="preserve">int</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr">
         <is>
-          <t>int</t>
+          <t xml:space="preserve">int</t>
         </is>
       </c>
       <c r="Q3" s="1" t="inlineStr">
         <is>
-          <t>int</t>
+          <t xml:space="preserve">int</t>
         </is>
       </c>
       <c r="R3" s="1" t="inlineStr">
         <is>
-          <t>vector2</t>
+          <t xml:space="preserve">vector2</t>
         </is>
       </c>
       <c r="S3" s="1" t="inlineStr">
         <is>
-          <t>vector2</t>
+          <t xml:space="preserve">vector2</t>
         </is>
       </c>
       <c r="T3" s="1" t="inlineStr">
         <is>
-          <t>vector2</t>
+          <t xml:space="preserve">vector2</t>
         </is>
       </c>
       <c r="U3" s="1" t="inlineStr">
         <is>
-          <t>float</t>
+          <t xml:space="preserve">float</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>##group</t>
+          <t xml:space="preserve">##group</t>
         </is>
       </c>
     </row>
     <row r="5" ht="112" customHeight="1">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>##</t>
+          <t xml:space="preserve">##</t>
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>攻击ID</t>
+          <t xml:space="preserve">攻击ID</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>旧 objattackDic 键名</t>
+          <t xml:space="preserve">旧 objattackDic 键名</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>中文名</t>
+          <t xml:space="preserve">中文名</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
-          <t>描述</t>
+          <t xml:space="preserve">描述</t>
         </is>
       </c>
       <c r="F5" s="1" t="inlineStr">
         <is>
-          <t>播放的动画名</t>
+          <t xml:space="preserve">播放的动画名</t>
         </is>
       </c>
       <c r="G5" s="1" t="inlineStr">
         <is>
-          <t>攻击力倍率范围(乘英雄攻击,X=下限,Y=上限,写法 1,1.2)</t>
+          <t xml:space="preserve">攻击力倍率范围(乘英雄攻击,X=下限,Y=上限,写法 1,1.2)</t>
         </is>
       </c>
       <c r="H5" s="1" t="inlineStr">
         <is>
-          <t>额外威力范围；英雄普攻 0,4 对应官方随机攻击，怪物填固定值范围</t>
+          <t xml:space="preserve">额外威力范围；英雄普攻 0,4 对应官方随机攻击，怪物填固定值范围</t>
         </is>
       </c>
       <c r="I5" s="1" t="inlineStr">
         <is>
-          <t>伤害类型</t>
+          <t xml:space="preserve">伤害类型</t>
         </is>
       </c>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>击退(X&gt;0=远离攻击者,Y&lt;0=向上;单位同旧 hurtBack,乘 BattleConfig.KnockbackScale* 换算 px/s,写法 2,0)</t>
+          <t xml:space="preserve">击退(X&gt;0=远离攻击者,Y&lt;0=向上;单位同旧 hurtBack,乘 BattleConfig.KnockbackScale* 换算 px/s,写法 2,0)</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>受击保护累计值(旧 HitProtect)</t>
+          <t xml:space="preserve">受击保护累计值(旧 HitProtect)</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
-          <t>起手音效(SoundConfig;None=无)</t>
+          <t xml:space="preserve">起手音效(SoundConfig;None=无)</t>
         </is>
       </c>
       <c r="M5" s="1" t="inlineStr">
         <is>
-          <t>命中音效(打中目标时播,None=无;旧项目按攻击者选音)</t>
+          <t xml:space="preserve">命中音效(打中目标时播,None=无;旧项目按攻击者选音)</t>
         </is>
       </c>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>这招属于谁(None=通用招,将来多主体共享用)</t>
+          <t xml:space="preserve">这招属于谁(None=通用招,将来多主体共享用)</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>连段第几段(0起;同一 OwnerId 内连续,越大越靠后)</t>
+          <t xml:space="preserve">连段第几段(0起;同一 OwnerId 内连续,越大越靠后)</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr">
         <is>
-          <t>AI 选招权重(怪物 AI 用;英雄普攻填 0)</t>
+          <t xml:space="preserve">AI 选招权重(怪物 AI 用;英雄普攻填 0)</t>
         </is>
       </c>
       <c r="Q5" s="1" t="inlineStr">
         <is>
-          <t>AI 优先级:0=普攻(按攻击欲望掷骰+权重抽);&gt;0=优先招(冷却就绪且够得着即先放,大者优先,接近途中也会放)</t>
+          <t xml:space="preserve">AI 优先级:0=普攻(按攻击欲望掷骰+权重抽);&gt;0=优先招(冷却就绪且够得着即先放,大者优先,接近途中也会放)</t>
         </is>
       </c>
       <c r="R5" s="1" t="inlineStr">
         <is>
-          <t>AI 释放距离 px(仅远程/无身体判定盒的招式;X=最小,Y=最大,只比水平距离;0,0=按攻击动画判定盒推导)</t>
+          <t xml:space="preserve">AI 释放距离 px(仅远程/无身体判定盒的招式;X=最小,Y=最大,只比水平距离;0,0=按攻击动画判定盒推导)</t>
         </is>
       </c>
       <c r="S5" s="1" t="inlineStr">
         <is>
-          <t>AI 释放后冷却秒(X=下限,Y=上限随机;普攻池填 0,0)</t>
+          <t xml:space="preserve">AI 释放后冷却秒(X=下限,Y=上限随机;普攻池填 0,0)</t>
         </is>
       </c>
       <c r="T5" s="1" t="inlineStr">
         <is>
-          <t>AI 出生时初始冷却秒(X=下限,Y=上限;旧 _ready 里 Skill_N_CD=randi_range)</t>
+          <t xml:space="preserve">AI 出生时初始冷却秒(X=下限,Y=上限;旧 _ready 里 Skill_N_CD=randi_range)</t>
         </is>
       </c>
       <c r="U5" s="1" t="inlineStr">
         <is>
-          <t>AI 收招硬直秒:收招后原地不动、不转身、不出招(英雄填 0)</t>
+          <t xml:space="preserve">AI 收招硬直秒:收招后原地不动、不转身、不出招(英雄填 0)</t>
         </is>
       </c>
     </row>
@@ -1401,62 +1329,56 @@
       <c r="B6" s="1" t="n">
         <v>1001</v>
       </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>role1.hit1</t>
-        </is>
+      <c r="C6" s="1" t="str">
+        <v>official.Role1.hit1</v>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>悟空普攻1</t>
+          <t xml:space="preserve">悟空普攻1</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
-          <t>普攻第一段</t>
+          <t xml:space="preserve">普攻第一段</t>
         </is>
       </c>
       <c r="F6" s="1" t="inlineStr">
         <is>
-          <t>attack_1</t>
+          <t xml:space="preserve">attack_1</t>
         </is>
       </c>
       <c r="G6" s="1" t="inlineStr">
         <is>
-          <t>1,1</t>
+          <t xml:space="preserve">1,1</t>
         </is>
       </c>
       <c r="H6" s="1" t="inlineStr">
         <is>
-          <t>0,4</t>
+          <t xml:space="preserve">0,4</t>
         </is>
       </c>
       <c r="I6" s="1" t="inlineStr">
         <is>
-          <t>Physics</t>
-        </is>
-      </c>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>2,0</t>
-        </is>
+          <t xml:space="preserve">Physics</t>
+        </is>
+      </c>
+      <c r="J6" s="1" t="str">
+        <v>0.5,-3</v>
       </c>
       <c r="K6" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="1" t="inlineStr">
-        <is>
-          <t>WukongAttack1And3</t>
-        </is>
+      <c r="L6" s="1" t="str">
+        <v>WukongAttack1And2</v>
       </c>
       <c r="M6" s="1" t="inlineStr">
         <is>
-          <t>WukongImpact</t>
+          <t xml:space="preserve">WukongImpact</t>
         </is>
       </c>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>Wukong</t>
+          <t xml:space="preserve">Wukong</t>
         </is>
       </c>
       <c r="O6" s="1" t="n">
@@ -1470,17 +1392,17 @@
       </c>
       <c r="R6" s="1" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t xml:space="preserve">0,0</t>
         </is>
       </c>
       <c r="S6" s="1" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t xml:space="preserve">0,0</t>
         </is>
       </c>
       <c r="T6" s="1" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t xml:space="preserve">0,0</t>
         </is>
       </c>
       <c r="U6" s="1" t="n">
@@ -1491,62 +1413,56 @@
       <c r="B7" s="1" t="n">
         <v>1002</v>
       </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>role1.hit2</t>
-        </is>
+      <c r="C7" s="1" t="str">
+        <v>official.Role1.hit2</v>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>悟空普攻2</t>
+          <t xml:space="preserve">悟空普攻2</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
-          <t>普攻第二段</t>
+          <t xml:space="preserve">普攻第二段</t>
         </is>
       </c>
       <c r="F7" s="1" t="inlineStr">
         <is>
-          <t>attack_2</t>
+          <t xml:space="preserve">attack_2</t>
         </is>
       </c>
       <c r="G7" s="1" t="inlineStr">
         <is>
-          <t>1,1</t>
+          <t xml:space="preserve">1,1</t>
         </is>
       </c>
       <c r="H7" s="1" t="inlineStr">
         <is>
-          <t>0,4</t>
+          <t xml:space="preserve">0,4</t>
         </is>
       </c>
       <c r="I7" s="1" t="inlineStr">
         <is>
-          <t>Physics</t>
-        </is>
-      </c>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>2,0</t>
-        </is>
+          <t xml:space="preserve">Physics</t>
+        </is>
+      </c>
+      <c r="J7" s="1" t="str">
+        <v>0.5,-3</v>
       </c>
       <c r="K7" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="1" t="inlineStr">
-        <is>
-          <t>WukongAttack2</t>
-        </is>
+      <c r="L7" s="1" t="str">
+        <v>WukongAttack1And2</v>
       </c>
       <c r="M7" s="1" t="inlineStr">
         <is>
-          <t>WukongImpact</t>
+          <t xml:space="preserve">WukongImpact</t>
         </is>
       </c>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>Wukong</t>
+          <t xml:space="preserve">Wukong</t>
         </is>
       </c>
       <c r="O7" s="1" t="n">
@@ -1560,17 +1476,17 @@
       </c>
       <c r="R7" s="1" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t xml:space="preserve">0,0</t>
         </is>
       </c>
       <c r="S7" s="1" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t xml:space="preserve">0,0</t>
         </is>
       </c>
       <c r="T7" s="1" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t xml:space="preserve">0,0</t>
         </is>
       </c>
       <c r="U7" s="1" t="n">
@@ -1581,62 +1497,56 @@
       <c r="B8" s="1" t="n">
         <v>1003</v>
       </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>role1.hit3</t>
-        </is>
+      <c r="C8" s="1" t="str">
+        <v>official.Role1.hit3</v>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>悟空普攻3</t>
+          <t xml:space="preserve">悟空普攻3</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr">
         <is>
-          <t>普攻第三段</t>
+          <t xml:space="preserve">普攻第三段</t>
         </is>
       </c>
       <c r="F8" s="1" t="inlineStr">
         <is>
-          <t>attack_3</t>
+          <t xml:space="preserve">attack_3</t>
         </is>
       </c>
       <c r="G8" s="1" t="inlineStr">
         <is>
-          <t>1,1</t>
+          <t xml:space="preserve">1,1</t>
         </is>
       </c>
       <c r="H8" s="1" t="inlineStr">
         <is>
-          <t>0,4</t>
+          <t xml:space="preserve">0,4</t>
         </is>
       </c>
       <c r="I8" s="1" t="inlineStr">
         <is>
-          <t>Physics</t>
-        </is>
-      </c>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>2,0</t>
-        </is>
+          <t xml:space="preserve">Physics</t>
+        </is>
+      </c>
+      <c r="J8" s="1" t="str">
+        <v>0.5,-3</v>
       </c>
       <c r="K8" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="1" t="inlineStr">
-        <is>
-          <t>WukongAttack1And3</t>
-        </is>
+      <c r="L8" s="1" t="str">
+        <v>WukongAttack3And4</v>
       </c>
       <c r="M8" s="1" t="inlineStr">
         <is>
-          <t>WukongImpact</t>
+          <t xml:space="preserve">WukongImpact</t>
         </is>
       </c>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>Wukong</t>
+          <t xml:space="preserve">Wukong</t>
         </is>
       </c>
       <c r="O8" s="1" t="n">
@@ -1650,17 +1560,17 @@
       </c>
       <c r="R8" s="1" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t xml:space="preserve">0,0</t>
         </is>
       </c>
       <c r="S8" s="1" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t xml:space="preserve">0,0</t>
         </is>
       </c>
       <c r="T8" s="1" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t xml:space="preserve">0,0</t>
         </is>
       </c>
       <c r="U8" s="1" t="n">
@@ -1671,62 +1581,54 @@
       <c r="B9" s="1" t="n">
         <v>1004</v>
       </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>role1.hit4</t>
-        </is>
+      <c r="C9" s="1" t="str">
+        <v>official.Role1.hit4</v>
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>悟空普攻4</t>
-        </is>
-      </c>
-      <c r="E9" s="1" t="inlineStr">
-        <is>
-          <t>普攻第四段(击退收招)</t>
-        </is>
+          <t xml:space="preserve">悟空普攻4</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="str">
+        <v>造一普攻第四段：旋身挥棍</v>
       </c>
       <c r="F9" s="1" t="inlineStr">
         <is>
-          <t>attack_4</t>
+          <t xml:space="preserve">attack_4</t>
         </is>
       </c>
       <c r="G9" s="1" t="inlineStr">
         <is>
-          <t>1,1</t>
+          <t xml:space="preserve">1,1</t>
         </is>
       </c>
       <c r="H9" s="1" t="inlineStr">
         <is>
-          <t>0,4</t>
+          <t xml:space="preserve">0,4</t>
         </is>
       </c>
       <c r="I9" s="1" t="inlineStr">
         <is>
-          <t>Physics</t>
-        </is>
-      </c>
-      <c r="J9" s="1" t="inlineStr">
-        <is>
-          <t>6,-5</t>
-        </is>
+          <t xml:space="preserve">Physics</t>
+        </is>
+      </c>
+      <c r="J9" s="1" t="str">
+        <v>0.5,-3</v>
       </c>
       <c r="K9" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="L9" s="1" t="inlineStr">
-        <is>
-          <t>WukongAttack4</t>
-        </is>
+      <c r="L9" s="1" t="str">
+        <v>WukongAttack3And4</v>
       </c>
       <c r="M9" s="1" t="inlineStr">
         <is>
-          <t>WukongImpact</t>
+          <t xml:space="preserve">WukongImpact</t>
         </is>
       </c>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>Wukong</t>
+          <t xml:space="preserve">Wukong</t>
         </is>
       </c>
       <c r="O9" s="1" t="n">
@@ -1740,17 +1642,17 @@
       </c>
       <c r="R9" s="1" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t xml:space="preserve">0,0</t>
         </is>
       </c>
       <c r="S9" s="1" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t xml:space="preserve">0,0</t>
         </is>
       </c>
       <c r="T9" s="1" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t xml:space="preserve">0,0</t>
         </is>
       </c>
       <c r="U9" s="1" t="n">
@@ -1763,42 +1665,42 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>monster1.hit1</t>
+          <t xml:space="preserve">monster1.hit1</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>猴子普攻</t>
+          <t xml:space="preserve">猴子普攻</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr">
         <is>
-          <t>猴子唯一攻击</t>
+          <t xml:space="preserve">猴子唯一攻击</t>
         </is>
       </c>
       <c r="F10" s="1" t="inlineStr">
         <is>
-          <t>attack_1</t>
+          <t xml:space="preserve">attack_1</t>
         </is>
       </c>
       <c r="G10" s="1" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t xml:space="preserve">0,0</t>
         </is>
       </c>
       <c r="H10" s="1" t="inlineStr">
         <is>
-          <t>5,5</t>
+          <t xml:space="preserve">5,5</t>
         </is>
       </c>
       <c r="I10" s="1" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t xml:space="preserve">Physics</t>
         </is>
       </c>
       <c r="J10" s="1" t="inlineStr">
         <is>
-          <t>2,-5</t>
+          <t xml:space="preserve">2,-5</t>
         </is>
       </c>
       <c r="K10" s="1" t="n">
@@ -1806,17 +1708,17 @@
       </c>
       <c r="L10" s="1" t="inlineStr">
         <is>
-          <t>None</t>
+          <t xml:space="preserve">None</t>
         </is>
       </c>
       <c r="M10" s="1" t="inlineStr">
         <is>
-          <t>None</t>
+          <t xml:space="preserve">None</t>
         </is>
       </c>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>HuaguoshanMonkey</t>
+          <t xml:space="preserve">HuaguoshanMonkey</t>
         </is>
       </c>
       <c r="O10" s="1" t="n">
@@ -1830,17 +1732,17 @@
       </c>
       <c r="R10" s="1" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t xml:space="preserve">0,0</t>
         </is>
       </c>
       <c r="S10" s="1" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t xml:space="preserve">0,0</t>
         </is>
       </c>
       <c r="T10" s="1" t="inlineStr">
         <is>
-          <t>0.5,1.0</t>
+          <t xml:space="preserve">0.5,1.0</t>
         </is>
       </c>
       <c r="U10" s="1" t="n">
@@ -1853,42 +1755,42 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>monster2.hit1</t>
+          <t xml:space="preserve">monster2.hit1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>妖猴普攻</t>
+          <t xml:space="preserve">妖猴普攻</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>站定后的普通攻击</t>
+          <t xml:space="preserve">站定后的普通攻击</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>attack_1</t>
+          <t xml:space="preserve">attack_1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t xml:space="preserve">0,0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>12,12</t>
+          <t xml:space="preserve">12,12</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t xml:space="preserve">Physics</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>6,-5</t>
+          <t xml:space="preserve">6,-5</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1896,17 +1798,17 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t xml:space="preserve">None</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t xml:space="preserve">None</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>DemonMonkey</t>
+          <t xml:space="preserve">DemonMonkey</t>
         </is>
       </c>
       <c r="O11" t="n">
@@ -1920,17 +1822,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t xml:space="preserve">0,0</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t xml:space="preserve">0,0</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>0.5,1.0</t>
+          <t xml:space="preserve">0.5,1.0</t>
         </is>
       </c>
       <c r="U11" t="n">
@@ -1943,42 +1845,42 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>official.Monster3.hit1</t>
+          <t xml:space="preserve">official.Monster3.hit1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>大猩猩重拳</t>
+          <t xml:space="preserve">大猩猩重拳</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>前摇抬拳后打出，结束后收招</t>
+          <t xml:space="preserve">前摇抬拳后打出，结束后收招</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>attack_1</t>
+          <t xml:space="preserve">attack_1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t xml:space="preserve">0,0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>20,20</t>
+          <t xml:space="preserve">20,20</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t xml:space="preserve">Physics</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>6,-5</t>
+          <t xml:space="preserve">6,-5</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1986,17 +1888,17 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>None</t>
+          <t xml:space="preserve">None</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>None</t>
+          <t xml:space="preserve">None</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Gorilla</t>
+          <t xml:space="preserve">Gorilla</t>
         </is>
       </c>
       <c r="O12" t="n">
@@ -2010,24 +1912,93 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t xml:space="preserve">0,0</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t xml:space="preserve">0,0</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>0.5,1.0</t>
+          <t xml:space="preserve">0.5,1.0</t>
         </is>
       </c>
       <c r="U12" t="n">
         <v>0.6</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1" t="n">
+        <v>1005</v>
+      </c>
+      <c r="C13" s="1" t="str">
+        <v>official.Role1.hit5</v>
+      </c>
+      <c r="D13" s="1" t="str">
+        <v>悟空普攻5</v>
+      </c>
+      <c r="E13" s="1" t="str">
+        <v>造一普攻第五段：终结击退</v>
+      </c>
+      <c r="F13" s="1" t="str">
+        <v>attack_5</v>
+      </c>
+      <c r="G13" s="1" t="str">
+        <v>1,1</v>
+      </c>
+      <c r="H13" s="1" t="str">
+        <v>0,4</v>
+      </c>
+      <c r="I13" s="1" t="str">
+        <v>Physics</v>
+      </c>
+      <c r="J13" s="1" t="str">
+        <v>25,-4</v>
+      </c>
+      <c r="K13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="1" t="str">
+        <v>WukongAttack5</v>
+      </c>
+      <c r="M13" s="1" t="str">
+        <v>WukongImpact</v>
+      </c>
+      <c r="N13" s="1" t="str">
+        <v>Wukong</v>
+      </c>
+      <c r="O13" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="P13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,0</t>
+        </is>
+      </c>
+      <c r="S13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,0</t>
+        </is>
+      </c>
+      <c r="T13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,0</t>
+        </is>
+      </c>
+      <c r="U13" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>